--- a/diseases/d131/2020-2025.xlsx
+++ b/diseases/d131/2020-2025.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9803,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9656,6 +9956,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9804,6 +10109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10396,6 +10721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10544,6 +10874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +11027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11284,6 +11639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +12098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +12251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12024,6 +12404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12172,6 +12557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +13016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12764,6 +13169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12912,6 +13322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13652,6 +14087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13800,6 +14240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14393,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14244,6 +14699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14392,6 +14852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14540,6 +15005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +15158,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14836,6 +15311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14984,6 +15464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15132,6 +15617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15280,6 +15770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15428,6 +15923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15576,6 +16076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15724,6 +16229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15872,6 +16382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16020,6 +16535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16168,6 +16688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16316,6 +16841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16464,6 +16994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16612,6 +17147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16760,6 +17300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16908,6 +17453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17056,6 +17606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17204,6 +17759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17500,6 +18065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17648,6 +18218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17796,6 +18371,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17944,6 +18524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18092,6 +18677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18240,6 +18830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18388,6 +18983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18536,6 +19136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18684,6 +19289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18832,6 +19442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18980,6 +19595,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19128,6 +19748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19276,6 +19901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19424,6 +20054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19572,6 +20207,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19720,6 +20360,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19868,6 +20513,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20016,6 +20666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20164,6 +20819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20312,6 +20972,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20460,6 +21125,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20608,6 +21278,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20756,6 +21431,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20904,6 +21584,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21052,6 +21737,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21200,6 +21890,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21348,6 +22043,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21496,6 +22196,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21644,6 +22349,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21792,6 +22502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21940,6 +22655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22088,6 +22808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22236,6 +22961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22384,6 +23114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22532,6 +23267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22680,6 +23420,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22828,6 +23573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22976,6 +23726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23124,6 +23879,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23272,6 +24032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23420,6 +24185,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23568,6 +24338,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23716,6 +24491,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23864,6 +24644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24012,6 +24797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24160,6 +24950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24308,6 +25103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +25256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24604,6 +25409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24752,6 +25562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24900,6 +25715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25048,6 +25868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25196,6 +26021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25344,6 +26174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25492,6 +26327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25640,6 +26480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25788,6 +26633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25936,6 +26786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26084,6 +26939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26232,6 +27092,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26380,6 +27245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26528,6 +27398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26676,6 +27551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26824,6 +27704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26972,6 +27857,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27120,6 +28010,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27268,6 +28163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27416,6 +28316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27564,6 +28469,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27712,6 +28622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27860,6 +28775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28008,6 +28928,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28156,6 +29081,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28304,6 +29234,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28452,6 +29387,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28600,6 +29540,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28748,6 +29693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28896,6 +29846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29044,6 +29999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29192,6 +30152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29340,6 +30305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29488,6 +30458,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29636,6 +30611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29784,6 +30764,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29932,6 +30917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30080,6 +31070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30228,6 +31223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30376,6 +31376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30524,6 +31529,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,6 +31682,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30820,6 +31835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30968,6 +31988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31116,6 +32141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31264,6 +32294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31412,6 +32447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31560,6 +32600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31708,6 +32753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31856,6 +32906,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32004,6 +33059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32152,6 +33212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32300,6 +33365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32448,6 +33518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32596,6 +33671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32744,6 +33824,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32892,6 +33977,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33040,6 +34130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33188,6 +34283,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33336,6 +34436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33484,6 +34589,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33632,6 +34742,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33780,6 +34895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33926,6 +35046,11 @@
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">

--- a/diseases/d131/2020-2025.xlsx
+++ b/diseases/d131/2020-2025.xlsx
@@ -4284,9 +4284,6 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -4743,9 +4740,6 @@
       <c r="O28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -5049,9 +5043,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -5814,9 +5805,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -5967,9 +5955,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -6273,9 +6258,6 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -6732,9 +6714,6 @@
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -7191,9 +7170,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -8262,9 +8238,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -8721,9 +8694,6 @@
       <c r="O54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -9027,9 +8997,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -9486,9 +9453,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -9639,9 +9603,6 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -9792,9 +9753,6 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -11016,9 +10974,6 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -11781,9 +11736,6 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -12240,9 +12192,6 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -12393,9 +12342,6 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -13005,9 +12951,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -13311,9 +13254,6 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -13464,9 +13404,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -14382,9 +14319,6 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -14841,9 +14775,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -14994,9 +14925,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -15606,9 +15534,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -16218,9 +16143,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -16371,9 +16293,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -16524,9 +16443,6 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -18054,9 +17970,6 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -18207,9 +18120,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -19278,9 +19188,6 @@
       <c r="O123" t="n">
         <v>2</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -19737,9 +19644,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -20502,9 +20406,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -20808,9 +20709,6 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -21114,9 +21012,6 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -24480,9 +24375,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -24786,9 +24678,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -24939,9 +24828,6 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -25245,9 +25131,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -25704,9 +25587,6 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -25857,9 +25737,6 @@
       <c r="O166" t="n">
         <v>2</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -26163,9 +26040,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -26316,9 +26190,6 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -26775,9 +26646,6 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -27234,9 +27102,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -28917,9 +28782,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -29682,9 +29544,6 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -30600,9 +30459,6 @@
       <c r="O197" t="n">
         <v>1</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -31671,9 +31527,6 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -33048,9 +32901,6 @@
       <c r="O213" t="n">
         <v>2</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -33354,9 +33204,6 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -34424,9 +34271,6 @@
       </c>
       <c r="O222" t="n">
         <v>1</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>0</v>
       </c>
       <c r="R222" t="n">
         <v>0.0002879555610852622</v>

--- a/diseases/d131/2020-2025.xlsx
+++ b/diseases/d131/2020-2025.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>2</v>
       </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.0005892124188649159</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -788,22 +786,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,17 +906,15 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0.000294606209432458</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -941,22 +927,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1071,17 +1047,15 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.000294606209432458</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1094,22 +1068,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1224,17 +1188,15 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.000294606209432458</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1247,22 +1209,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,17 +1329,15 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.000294606209432458</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1400,22 +1350,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1530,17 +1470,15 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.000294606209432458</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1553,22 +1491,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1683,17 +1611,15 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.000294606209432458</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1706,22 +1632,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1836,17 +1752,15 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.000294606209432458</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1859,22 +1773,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1989,17 +1893,15 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.000294606209432458</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2012,22 +1914,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2142,17 +2034,15 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.000293978058494878</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2165,22 +2055,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2295,17 +2175,15 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.000293978058494878</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2318,22 +2196,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2448,17 +2316,15 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.000293978058494878</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2471,22 +2337,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2601,17 +2457,15 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.000293978058494878</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2624,22 +2478,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2754,17 +2598,15 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.000293978058494878</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2777,22 +2619,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2907,17 +2739,15 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.000293978058494878</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2930,22 +2760,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3060,17 +2880,15 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.000293978058494878</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3083,22 +2901,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3213,17 +3021,15 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3236,22 +3042,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3366,17 +3162,15 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3389,22 +3183,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3519,17 +3303,15 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3542,22 +3324,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3672,17 +3444,15 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3695,22 +3465,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3825,17 +3585,15 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3848,22 +3606,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3978,17 +3726,15 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4001,22 +3747,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4131,17 +3867,15 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4154,22 +3888,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4284,14 +4008,12 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
       <c r="R25" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4304,22 +4026,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4434,17 +4146,15 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4457,22 +4167,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4587,17 +4287,15 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4610,22 +4308,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4740,14 +4428,12 @@
       <c r="O28" t="n">
         <v>2</v>
       </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
       <c r="R28" t="n">
         <v>0.000585593157212785</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4760,22 +4446,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4890,17 +4566,15 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4913,22 +4587,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5043,14 +4707,12 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5063,22 +4725,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5193,17 +4845,15 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5216,22 +4866,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5346,17 +4986,15 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5369,22 +5007,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5499,17 +5127,15 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5522,22 +5148,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5652,17 +5268,15 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5675,22 +5289,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5805,14 +5409,12 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5825,22 +5427,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5955,14 +5547,12 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5975,22 +5565,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6105,17 +5685,15 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6128,22 +5706,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6258,14 +5826,12 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
       <c r="R38" t="n">
         <v>0.000585593157212785</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6278,22 +5844,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6408,17 +5964,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6431,22 +5985,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6561,17 +6105,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6584,22 +6126,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6714,14 +6246,12 @@
       <c r="O41" t="n">
         <v>1</v>
       </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6734,22 +6264,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6864,17 +6384,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6887,22 +6405,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7017,17 +6525,15 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7040,22 +6546,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7170,14 +6666,12 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
       <c r="R44" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7190,22 +6684,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7320,17 +6804,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7343,22 +6825,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7473,17 +6945,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7496,22 +6966,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7626,17 +7086,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7649,22 +7107,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7779,17 +7227,15 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7802,22 +7248,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7932,17 +7368,15 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7955,22 +7389,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8085,17 +7509,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8108,22 +7530,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8238,14 +7650,12 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
       <c r="R51" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8258,22 +7668,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8388,17 +7788,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8411,22 +7809,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8541,17 +7929,15 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8564,22 +7950,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8694,14 +8070,12 @@
       <c r="O54" t="n">
         <v>2</v>
       </c>
+      <c r="P54" t="n">
+        <v>2</v>
+      </c>
       <c r="R54" t="n">
         <v>0.000585593157212785</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8714,22 +8088,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8844,17 +8208,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8867,22 +8229,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8997,14 +8349,12 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
       <c r="R56" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9017,22 +8367,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9147,17 +8487,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9170,22 +8508,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9300,17 +8628,15 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9323,22 +8649,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9453,14 +8769,12 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
       <c r="R59" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9473,22 +8787,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9603,14 +8907,12 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
+      <c r="P60" t="n">
+        <v>2</v>
+      </c>
       <c r="R60" t="n">
         <v>0.000585593157212785</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9623,22 +8925,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9753,14 +9045,12 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
       <c r="R61" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9773,22 +9063,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9903,17 +9183,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9926,22 +9204,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10056,17 +9324,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10079,22 +9345,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10209,17 +9465,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10232,22 +9486,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10362,17 +9606,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10385,22 +9627,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10515,17 +9747,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10538,22 +9768,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10668,17 +9888,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10691,22 +9909,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10821,17 +10029,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10844,22 +10050,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10974,14 +10170,12 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
       <c r="R69" t="n">
         <v>0.0002927965786063925</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10994,22 +10188,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11124,17 +10308,15 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11147,22 +10329,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11277,17 +10449,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11300,22 +10470,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11430,17 +10590,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11453,22 +10611,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11583,17 +10731,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11606,22 +10752,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11736,14 +10872,12 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
+      <c r="P74" t="n">
+        <v>2</v>
+      </c>
       <c r="R74" t="n">
         <v>0.0005822800505890731</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11756,22 +10890,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11886,17 +11010,15 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11909,22 +11031,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12039,17 +11151,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12062,22 +11172,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12192,14 +11292,12 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
       <c r="R77" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12212,22 +11310,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12342,14 +11430,12 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
       <c r="R78" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12362,22 +11448,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12492,17 +11568,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12515,22 +11589,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12645,17 +11709,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12668,22 +11730,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12798,17 +11850,15 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12821,22 +11871,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12951,14 +11991,12 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
       <c r="R82" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12971,22 +12009,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13101,17 +12129,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13124,22 +12150,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13254,14 +12270,12 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
+      <c r="P84" t="n">
+        <v>2</v>
+      </c>
       <c r="R84" t="n">
         <v>0.0005822800505890731</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13274,22 +12288,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13404,14 +12408,12 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
       <c r="R85" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13424,22 +12426,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13554,17 +12546,15 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13577,22 +12567,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13707,17 +12687,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13730,22 +12708,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13860,17 +12828,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13883,22 +12849,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14013,17 +12969,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14036,22 +12990,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14166,17 +13110,15 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14189,22 +13131,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14319,14 +13251,12 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
       <c r="R91" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14339,22 +13269,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14469,17 +13389,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14492,22 +13410,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14622,17 +13530,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14645,22 +13551,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14775,14 +13671,12 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
       <c r="R94" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14795,22 +13689,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14925,14 +13809,12 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
       <c r="R95" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14945,22 +13827,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15075,17 +13947,15 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15098,22 +13968,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15228,17 +14088,15 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15251,22 +14109,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15381,17 +14229,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15404,22 +14250,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15534,14 +14370,12 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
+      <c r="P99" t="n">
+        <v>1</v>
+      </c>
       <c r="R99" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15554,22 +14388,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15684,17 +14508,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15707,22 +14529,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15837,17 +14649,15 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15860,22 +14670,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15990,17 +14790,15 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16013,22 +14811,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16143,14 +14931,12 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
+      <c r="P103" t="n">
+        <v>2</v>
+      </c>
       <c r="R103" t="n">
         <v>0.0005822800505890731</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16163,22 +14949,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16293,14 +15069,12 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
       <c r="R104" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16313,22 +15087,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16443,14 +15207,12 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
       <c r="R105" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16463,22 +15225,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16593,17 +15345,15 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16616,22 +15366,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16746,17 +15486,15 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16769,22 +15507,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16899,17 +15627,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16922,22 +15648,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -17052,17 +15768,15 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17075,22 +15789,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17205,17 +15909,15 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17228,22 +15930,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17358,17 +16050,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17381,22 +16071,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17511,17 +16191,15 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17534,22 +16212,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17664,17 +16332,15 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17687,22 +16353,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17817,17 +16473,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17840,22 +16494,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17970,14 +16614,12 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
       <c r="R115" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17990,22 +16632,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18120,14 +16752,12 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
       <c r="R116" t="n">
         <v>0.0002911400252945365</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18140,22 +16770,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18270,17 +16890,15 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18293,22 +16911,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18423,17 +17031,15 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18446,22 +17052,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18576,17 +17172,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18599,22 +17193,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18729,17 +17313,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18752,22 +17334,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18882,17 +17454,15 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18905,22 +17475,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19035,17 +17595,15 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19058,22 +17616,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -19188,14 +17736,12 @@
       <c r="O123" t="n">
         <v>2</v>
       </c>
+      <c r="P123" t="n">
+        <v>2</v>
+      </c>
       <c r="R123" t="n">
         <v>0.0005789942546139568</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19208,22 +17754,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19338,17 +17874,15 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19361,22 +17895,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19491,17 +18015,15 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19514,22 +18036,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19644,14 +18156,12 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
       <c r="R126" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19664,22 +18174,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19794,17 +18294,15 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19817,22 +18315,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19947,17 +18435,15 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19970,22 +18456,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20100,17 +18576,15 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20123,22 +18597,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -20253,17 +18717,15 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20276,22 +18738,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20406,14 +18858,12 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
+      <c r="P131" t="n">
+        <v>1</v>
+      </c>
       <c r="R131" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20426,22 +18876,12 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20556,17 +18996,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20579,22 +19017,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20709,14 +19137,12 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
       <c r="R133" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20729,22 +19155,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -20859,17 +19275,15 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20882,22 +19296,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -21012,14 +19416,12 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
       <c r="R135" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21032,22 +19434,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21162,17 +19554,15 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21185,22 +19575,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21315,17 +19695,15 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21338,22 +19716,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21468,17 +19836,15 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21491,22 +19857,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21621,17 +19977,15 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21644,22 +19998,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -21774,17 +20118,15 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21797,22 +20139,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -21927,17 +20259,15 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21950,22 +20280,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22080,17 +20400,15 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22103,22 +20421,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22233,17 +20541,15 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22256,22 +20562,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22386,17 +20682,15 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22409,22 +20703,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -22539,17 +20823,15 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22562,22 +20844,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -22692,17 +20964,15 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22715,22 +20985,12 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -22845,17 +21105,15 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22868,22 +21126,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -22998,17 +21246,15 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23021,22 +21267,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23151,17 +21387,15 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23174,22 +21408,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23304,17 +21528,15 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23327,22 +21549,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -23457,17 +21669,15 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23480,22 +21690,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -23610,17 +21810,15 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23633,22 +21831,12 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -23763,17 +21951,15 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23786,22 +21972,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -23916,17 +22092,15 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23939,22 +22113,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24069,17 +22233,15 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24092,22 +22254,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -24222,17 +22374,15 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24245,22 +22395,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -24375,14 +22515,12 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
+      <c r="P157" t="n">
+        <v>1</v>
+      </c>
       <c r="R157" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24395,22 +22533,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24525,17 +22653,15 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24548,22 +22674,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -24678,14 +22794,12 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
+      <c r="P159" t="n">
+        <v>1</v>
+      </c>
       <c r="R159" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24698,22 +22812,12 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -24828,14 +22932,12 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
+      <c r="P160" t="n">
+        <v>1</v>
+      </c>
       <c r="R160" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24848,22 +22950,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -24978,17 +23070,15 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25001,22 +23091,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -25131,14 +23211,12 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
+      <c r="P162" t="n">
+        <v>1</v>
+      </c>
       <c r="R162" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25151,22 +23229,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25281,17 +23349,15 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25304,22 +23370,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25434,17 +23490,15 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25457,22 +23511,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25587,14 +23631,12 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
+      <c r="P165" t="n">
+        <v>1</v>
+      </c>
       <c r="R165" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25607,22 +23649,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -25737,14 +23769,12 @@
       <c r="O166" t="n">
         <v>2</v>
       </c>
+      <c r="P166" t="n">
+        <v>2</v>
+      </c>
       <c r="R166" t="n">
         <v>0.0005789942546139568</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25757,22 +23787,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -25887,17 +23907,15 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25910,22 +23928,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -26040,14 +24048,12 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
+      <c r="P168" t="n">
+        <v>1</v>
+      </c>
       <c r="R168" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26060,22 +24066,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -26190,14 +24186,12 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
+      <c r="P169" t="n">
+        <v>1</v>
+      </c>
       <c r="R169" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26210,22 +24204,12 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26340,17 +24324,15 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26363,22 +24345,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26493,17 +24465,15 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26516,22 +24486,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -26646,14 +24606,12 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
+      <c r="P172" t="n">
+        <v>1</v>
+      </c>
       <c r="R172" t="n">
         <v>0.0002894971273069784</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26666,22 +24624,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -26796,17 +24744,15 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26819,22 +24765,12 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -26949,17 +24885,15 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26972,22 +24906,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -27102,14 +25026,12 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
+      <c r="P175" t="n">
+        <v>1</v>
+      </c>
       <c r="R175" t="n">
         <v>0.0002879555610852622</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27122,22 +25044,12 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -27252,17 +25164,15 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27275,22 +25185,12 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -27405,17 +25305,15 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27428,22 +25326,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -27558,17 +25446,15 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27581,22 +25467,12 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -27711,17 +25587,15 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27734,22 +25608,12 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -27864,17 +25728,15 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27887,22 +25749,12 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -28017,17 +25869,15 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28040,22 +25890,12 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -28170,17 +26010,15 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
       <c r="Q182" t="n">
         <v>0</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28193,22 +26031,12 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
         <v>0</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -28323,17 +26151,15 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28346,22 +26172,12 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -28476,17 +26292,15 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
       <c r="Q184" t="n">
         <v>0</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28499,22 +26313,12 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -28629,17 +26433,15 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
       <c r="Q185" t="n">
         <v>0</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28652,22 +26454,12 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -28782,14 +26574,12 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
+      <c r="P186" t="n">
+        <v>1</v>
+      </c>
       <c r="R186" t="n">
         <v>0.0002879555610852622</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28802,22 +26592,12 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -28932,17 +26712,15 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
       <c r="Q187" t="n">
         <v>0</v>
       </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28955,22 +26733,12 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -29085,17 +26853,15 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
       <c r="Q188" t="n">
         <v>0</v>
       </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29108,22 +26874,12 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
-      </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -29238,17 +26994,15 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
       <c r="Q189" t="n">
         <v>0</v>
       </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29261,22 +27015,12 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -29391,17 +27135,15 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
       <c r="Q190" t="n">
         <v>0</v>
       </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29414,22 +27156,12 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -29544,14 +27276,12 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
+      <c r="P191" t="n">
+        <v>1</v>
+      </c>
       <c r="R191" t="n">
         <v>0.0002879555610852622</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29564,22 +27294,12 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -29694,17 +27414,15 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
       <c r="Q192" t="n">
         <v>0</v>
       </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29717,22 +27435,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -29847,17 +27555,15 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
       <c r="Q193" t="n">
         <v>0</v>
       </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29870,22 +27576,12 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -30000,17 +27696,15 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
       <c r="Q194" t="n">
         <v>0</v>
       </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30023,22 +27717,12 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
-      </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -30153,17 +27837,15 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30176,22 +27858,12 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
-      </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -30306,17 +27978,15 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30329,22 +27999,12 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
         <v>0</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -30459,14 +28119,12 @@
       <c r="O197" t="n">
         <v>1</v>
       </c>
+      <c r="P197" t="n">
+        <v>1</v>
+      </c>
       <c r="R197" t="n">
         <v>0.0002879555610852622</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30479,22 +28137,12 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -30609,17 +28257,15 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
       <c r="Q198" t="n">
         <v>0</v>
       </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30632,22 +28278,12 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -30762,17 +28398,15 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
       <c r="Q199" t="n">
         <v>0</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30785,22 +28419,12 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -30915,17 +28539,15 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
       <c r="Q200" t="n">
         <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30938,22 +28560,12 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -31068,17 +28680,15 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
       <c r="Q201" t="n">
         <v>0</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31091,22 +28701,12 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
         <v>0</v>
-      </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -31221,17 +28821,15 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
       <c r="Q202" t="n">
         <v>0</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31244,22 +28842,12 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
         <v>0</v>
-      </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -31374,17 +28962,15 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31397,22 +28983,12 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -31527,14 +29103,12 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
+      <c r="P204" t="n">
+        <v>1</v>
+      </c>
       <c r="R204" t="n">
         <v>0.0002879555610852622</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31547,22 +29121,12 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
-      </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -31677,17 +29241,15 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
+      <c r="P205" t="n">
+        <v>0</v>
+      </c>
       <c r="Q205" t="n">
         <v>0</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31700,22 +29262,12 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -31830,17 +29382,15 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
       <c r="Q206" t="n">
         <v>0</v>
       </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31853,22 +29403,12 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
         <v>0</v>
-      </c>
-      <c r="AU206" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
@@ -31983,17 +29523,15 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
       <c r="Q207" t="n">
         <v>0</v>
       </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32006,22 +29544,12 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
         <v>0</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -32136,17 +29664,15 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
       <c r="Q208" t="n">
         <v>0</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32159,22 +29685,12 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
-      </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
@@ -32289,17 +29805,15 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
       <c r="Q209" t="n">
         <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32312,22 +29826,12 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
         <v>0</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -32442,17 +29946,15 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
       <c r="Q210" t="n">
         <v>0</v>
       </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32465,22 +29967,12 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
-      </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
@@ -32595,17 +30087,15 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32618,22 +30108,12 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
         <v>0</v>
-      </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -32748,17 +30228,15 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
       <c r="Q212" t="n">
         <v>0</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32771,22 +30249,12 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
-      </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -32901,14 +30369,12 @@
       <c r="O213" t="n">
         <v>2</v>
       </c>
+      <c r="P213" t="n">
+        <v>2</v>
+      </c>
       <c r="R213" t="n">
         <v>0.0005759111221705244</v>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32921,22 +30387,12 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
         <v>0</v>
-      </c>
-      <c r="AU213" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
@@ -33051,17 +30507,15 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
       <c r="Q214" t="n">
         <v>0</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33074,22 +30528,12 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
         <v>0</v>
-      </c>
-      <c r="AU214" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
@@ -33204,14 +30648,12 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
+      <c r="P215" t="n">
+        <v>1</v>
+      </c>
       <c r="R215" t="n">
         <v>0.0002879555610852622</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33224,22 +30666,12 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -33354,17 +30786,15 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
       <c r="Q216" t="n">
         <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33377,22 +30807,12 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
-      </c>
-      <c r="AU216" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
@@ -33507,17 +30927,15 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
       <c r="Q217" t="n">
         <v>0</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33530,22 +30948,12 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
         <v>0</v>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -33660,17 +31068,15 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33683,22 +31089,12 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -33813,17 +31209,15 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
       <c r="Q219" t="n">
         <v>0</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33836,22 +31230,12 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
         <v>0</v>
-      </c>
-      <c r="AU219" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -33966,17 +31350,15 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
       <c r="Q220" t="n">
         <v>0</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33989,22 +31371,12 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
         <v>0</v>
-      </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
@@ -34119,17 +31491,15 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
       <c r="Q221" t="n">
         <v>0</v>
       </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34142,22 +31512,12 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
         <v>0</v>
-      </c>
-      <c r="AU221" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
@@ -34272,14 +31632,12 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
+      <c r="P222" t="n">
+        <v>1</v>
+      </c>
       <c r="R222" t="n">
         <v>0.0002879555610852622</v>
       </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34292,22 +31650,12 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
-      </c>
-      <c r="AU222" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
@@ -34422,17 +31770,15 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
       <c r="Q223" t="n">
         <v>0</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34445,22 +31791,12 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
-      </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -34575,17 +31911,15 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
       <c r="Q224" t="n">
         <v>0</v>
       </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34598,22 +31932,12 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
-      </c>
-      <c r="AU224" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -34728,17 +32052,15 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
       <c r="Q225" t="n">
         <v>0</v>
       </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34751,22 +32073,12 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
         <v>0</v>
-      </c>
-      <c r="AU225" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
@@ -34881,17 +32193,15 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34904,22 +32214,12 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
         <v>0</v>
-      </c>
-      <c r="AU226" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
